--- a/config/card_ability.xlsx
+++ b/config/card_ability.xlsx
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>突撃の怒り</t>
+          <t>愤怒的突击</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AC8" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AC13" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="AC14" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>猛烈衝撃</t>
+          <t>猛烈冲击</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>防御の怒り</t>
+          <t>愤怒的防御</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AC17" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AC18" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AC20" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AC21" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC23" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AC24" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>難攻不落</t>
+          <t>坚不可摧</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>掌握の怒り</t>
+          <t>愤怒的掌控</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AC27" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AC28" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AC30" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AC31" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC33" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="AC34" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>戦場掌握</t>
+          <t>战场控制</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>先制の怒り</t>
+          <t>先发制人的愤怒</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AC37" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="AC38" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AC39" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AC40" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="AC43" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC44" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>追加ダメージ</t>
+          <t>额外伤害</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>修練の怒り</t>
+          <t>修炼的愤怒</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="AC47" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AC48" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="AC49" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="AC50" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="AC53" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AC54" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>突撃の怒り</t>
+          <t>愤怒的突击</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="H57" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="AC57" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AC58" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="AC59" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AC60" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AC63" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="AC64" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>猛烈衝撃</t>
+          <t>猛烈冲击</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>防御の怒り</t>
+          <t>愤怒的防御</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="AC67" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AC68" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AC70" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AC71" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="AC73" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="AC74" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>難攻不落</t>
+          <t>坚不可摧</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>掌握の怒り</t>
+          <t>愤怒的掌控</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="AC77" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AC78" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="AC80" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="AC81" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="AC83" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="AC84" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>戦場掌握</t>
+          <t>战场控制</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>先制の怒り</t>
+          <t>先发制人的愤怒</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="AC87" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="AC88" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="AC89" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="AC90" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="AC93" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="AC94" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>追加ダメージ</t>
+          <t>额外伤害</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>修練の怒り</t>
+          <t>修炼的愤怒</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="AC97" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="AC98" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="AC99" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="AC100" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -15179,7 +15179,7 @@
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="AC103" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="AC104" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>突撃の怒り</t>
+          <t>愤怒的突击</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AC108" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="AC109" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AC110" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -16197,7 +16197,7 @@
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -16297,7 +16297,7 @@
       </c>
       <c r="AC111" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="H114" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AC114" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="H115" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AC115" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H116" s="1" t="inlineStr">
         <is>
-          <t>猛烈衝撃</t>
+          <t>猛烈冲击</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H117" s="1" t="inlineStr">
         <is>
-          <t>防御の怒り</t>
+          <t>愤怒的防御</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="H118" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -17236,7 +17236,7 @@
       </c>
       <c r="AC118" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="H119" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AC119" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H120" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H121" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="AC121" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="H122" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="AC122" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -17998,7 +17998,7 @@
       </c>
       <c r="H124" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="AC124" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="H125" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="AC125" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -18297,7 +18297,7 @@
       </c>
       <c r="H126" s="1" t="inlineStr">
         <is>
-          <t>難攻不落</t>
+          <t>坚不可摧</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="H127" s="1" t="inlineStr">
         <is>
-          <t>掌握の怒り</t>
+          <t>愤怒的掌控</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="H128" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="AC128" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="H129" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -18793,7 +18793,7 @@
       </c>
       <c r="AC129" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="H130" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="H131" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="AC131" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="H132" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="AC132" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="AC134" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="AC135" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -19697,7 +19697,7 @@
       </c>
       <c r="H136" s="1" t="inlineStr">
         <is>
-          <t>戦場掌握</t>
+          <t>战场控制</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="H137" s="1" t="inlineStr">
         <is>
-          <t>先制の怒り</t>
+          <t>先发制人的愤怒</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -19936,7 +19936,7 @@
       </c>
       <c r="H138" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="AC138" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="H139" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="AC139" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="H140" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -20340,7 +20340,7 @@
       </c>
       <c r="AC140" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="H141" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -20497,7 +20497,7 @@
       </c>
       <c r="AC141" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="H142" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -20798,7 +20798,7 @@
       </c>
       <c r="H144" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="AC144" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="H145" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="AC145" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -21097,7 +21097,7 @@
       </c>
       <c r="H146" s="1" t="inlineStr">
         <is>
-          <t>追加ダメージ</t>
+          <t>额外伤害</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="H147" s="1" t="inlineStr">
         <is>
-          <t>修練の怒り</t>
+          <t>修炼的愤怒</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -21336,7 +21336,7 @@
       </c>
       <c r="H148" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="AC148" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="H149" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="AC149" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -21640,7 +21640,7 @@
       </c>
       <c r="H150" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="AC150" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="H151" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -21897,7 +21897,7 @@
       </c>
       <c r="AC151" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="H152" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="H154" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="AC154" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -22345,7 +22345,7 @@
       </c>
       <c r="H155" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="AC155" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="H157" s="1" t="inlineStr">
         <is>
-          <t>突撃の怒り</t>
+          <t>愤怒的突击</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="H158" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="AC158" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -22903,7 +22903,7 @@
       </c>
       <c r="H159" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="AC159" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="H160" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="AC160" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -23207,7 +23207,7 @@
       </c>
       <c r="H161" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="AC161" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="H162" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="H164" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="AC164" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="H165" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="AC165" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="H166" s="1" t="inlineStr">
         <is>
-          <t>猛烈衝撃</t>
+          <t>猛烈冲击</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="H167" s="1" t="inlineStr">
         <is>
-          <t>防御の怒り</t>
+          <t>愤怒的防御</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="H168" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="AC168" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -24303,7 +24303,7 @@
       </c>
       <c r="H169" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="AC169" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="H170" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="H171" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -24672,7 +24672,7 @@
       </c>
       <c r="AC171" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -24729,7 +24729,7 @@
       </c>
       <c r="H172" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="AC172" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="H174" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="AC174" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="H175" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="AC175" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="H176" s="1" t="inlineStr">
         <is>
-          <t>難攻不落</t>
+          <t>坚不可摧</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -25429,7 +25429,7 @@
       </c>
       <c r="H177" s="1" t="inlineStr">
         <is>
-          <t>掌握の怒り</t>
+          <t>愤怒的掌控</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -25546,7 +25546,7 @@
       </c>
       <c r="H178" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="AC178" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -25703,7 +25703,7 @@
       </c>
       <c r="H179" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="AC179" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="H180" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="H181" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="AC181" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -26129,7 +26129,7 @@
       </c>
       <c r="H182" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -26229,7 +26229,7 @@
       </c>
       <c r="AC182" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="H184" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -26498,7 +26498,7 @@
       </c>
       <c r="AC184" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -26555,7 +26555,7 @@
       </c>
       <c r="H185" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="AC185" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -26707,7 +26707,7 @@
       </c>
       <c r="H186" s="1" t="inlineStr">
         <is>
-          <t>戦場掌握</t>
+          <t>战场控制</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -26829,7 +26829,7 @@
       </c>
       <c r="H187" s="1" t="inlineStr">
         <is>
-          <t>先制の怒り</t>
+          <t>先发制人的愤怒</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="H188" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="AC188" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -27103,7 +27103,7 @@
       </c>
       <c r="H189" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -27203,7 +27203,7 @@
       </c>
       <c r="AC189" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="H190" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="AC190" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -27407,7 +27407,7 @@
       </c>
       <c r="H191" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -27507,7 +27507,7 @@
       </c>
       <c r="AC191" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -27564,7 +27564,7 @@
       </c>
       <c r="H192" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="H194" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -27898,7 +27898,7 @@
       </c>
       <c r="AC194" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -27955,7 +27955,7 @@
       </c>
       <c r="H195" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -28045,7 +28045,7 @@
       </c>
       <c r="AC195" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="H196" s="1" t="inlineStr">
         <is>
-          <t>追加ダメージ</t>
+          <t>额外伤害</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="H197" s="1" t="inlineStr">
         <is>
-          <t>修練の怒り</t>
+          <t>修炼的愤怒</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="H198" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -28436,7 +28436,7 @@
       </c>
       <c r="AC198" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -28493,7 +28493,7 @@
       </c>
       <c r="H199" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -28593,7 +28593,7 @@
       </c>
       <c r="AC199" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -28650,7 +28650,7 @@
       </c>
       <c r="H200" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="AC200" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -28807,7 +28807,7 @@
       </c>
       <c r="H201" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -28907,7 +28907,7 @@
       </c>
       <c r="AC201" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="H202" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -29208,7 +29208,7 @@
       </c>
       <c r="H204" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -29298,7 +29298,7 @@
       </c>
       <c r="AC204" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
@@ -29355,7 +29355,7 @@
       </c>
       <c r="H205" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -29455,7 +29455,7 @@
       </c>
       <c r="AC205" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="H208" s="1" t="inlineStr">
         <is>
-          <t>先制の怒り</t>
+          <t>先发制人的愤怒</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -29765,7 +29765,7 @@
       </c>
       <c r="H209" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -29865,7 +29865,7 @@
       </c>
       <c r="AC209" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -29922,7 +29922,7 @@
       </c>
       <c r="H210" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -30022,7 +30022,7 @@
       </c>
       <c r="AC210" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -30079,7 +30079,7 @@
       </c>
       <c r="H211" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="AC211" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -30226,7 +30226,7 @@
       </c>
       <c r="H212" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="AC212" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -30383,7 +30383,7 @@
       </c>
       <c r="H213" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -30627,7 +30627,7 @@
       </c>
       <c r="H215" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -30717,7 +30717,7 @@
       </c>
       <c r="AC215" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -30774,7 +30774,7 @@
       </c>
       <c r="H216" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -30864,7 +30864,7 @@
       </c>
       <c r="AC216" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="H217" s="1" t="inlineStr">
         <is>
-          <t>追加ダメージ</t>
+          <t>额外伤害</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="H219" s="1" t="inlineStr">
         <is>
-          <t>掌握の怒り</t>
+          <t>愤怒的掌控</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -31174,7 +31174,7 @@
       </c>
       <c r="H220" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -31274,7 +31274,7 @@
       </c>
       <c r="AC220" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="H221" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -31431,7 +31431,7 @@
       </c>
       <c r="AC221" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -31488,7 +31488,7 @@
       </c>
       <c r="H222" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="H223" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -31700,7 +31700,7 @@
       </c>
       <c r="AC223" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -31757,7 +31757,7 @@
       </c>
       <c r="H224" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -31857,7 +31857,7 @@
       </c>
       <c r="AC224" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="H226" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -32126,7 +32126,7 @@
       </c>
       <c r="AC226" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -32183,7 +32183,7 @@
       </c>
       <c r="H227" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="AC227" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -32335,7 +32335,7 @@
       </c>
       <c r="H228" s="1" t="inlineStr">
         <is>
-          <t>戦場掌握</t>
+          <t>战场控制</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -32466,7 +32466,7 @@
       </c>
       <c r="H230" s="1" t="inlineStr">
         <is>
-          <t>掌握の怒り</t>
+          <t>愤怒的掌控</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="H231" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="AC231" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="H232" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="AC232" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr">
@@ -32897,7 +32897,7 @@
       </c>
       <c r="H233" s="1" t="inlineStr">
         <is>
-          <t>通常攻撃強化</t>
+          <t>普通攻击强化</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -33019,7 +33019,7 @@
       </c>
       <c r="H234" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -33109,7 +33109,7 @@
       </c>
       <c r="AC234" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -33166,7 +33166,7 @@
       </c>
       <c r="H235" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="AC235" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇\n%sが%s上昇</t>
+          <t>%s上升%s\n%s上升%s</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -33445,7 +33445,7 @@
       </c>
       <c r="H237" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -33535,7 +33535,7 @@
       </c>
       <c r="AC237" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -33592,7 +33592,7 @@
       </c>
       <c r="H238" s="1" t="inlineStr">
         <is>
-          <t>基礎潜能</t>
+          <t>基础潜能</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="AC238" s="1" t="inlineStr">
         <is>
-          <t>%sが%s上昇</t>
+          <t>%s上升%s</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -33744,7 +33744,7 @@
       </c>
       <c r="H239" s="1" t="inlineStr">
         <is>
-          <t>戦場掌握</t>
+          <t>战场控制</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
